--- a/光伏配储项目/电价数据/2026/黄埔B厂.xlsx
+++ b/光伏配储项目/电价数据/2026/黄埔B厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5376000000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6643300000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.19432</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.94665</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.84585</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44203</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47699</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.96546</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.74099</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.61326</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.52279</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.71269</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7433200000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.88773</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.4974</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.54153</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.53394</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.9316599999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.6030800000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.12079</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.75221</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.73891</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.76232</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.77508</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.97577</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>1.47812</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.53196</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.75409</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>1.18535</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74846</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>1.06684</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.95643</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.97894</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.28325</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.27999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.26275</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7553</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.31482</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.15205</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.8476</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.15566</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.42053</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.20093</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.47119</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.67643</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.7922400000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.42082</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.5992</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.6311</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.21123</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.42982</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.21306</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.65463</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.37584</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.33884</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.31314</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8243400000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47976</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40641</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42181</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.24822</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.02131</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.05986</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5377999999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52278</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5701799999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49908</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47325</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5512999999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7637999999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.73265</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46082</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43262</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>1.02572</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.13005</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7687999999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.81902</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.9740700000000001</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.95977</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.77015</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5305800000000001</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.92502</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.21166</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.49694</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.47397</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.4211</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.31091</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.33621</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.50218</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.67915</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.49658</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.51171</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.1794</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.11773</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.14392</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.09713</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.90073</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.22908</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.2358</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.97204</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.95724</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.36634</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.50292</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.27118</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.99836</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.77671</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.94136</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.43107</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44082</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.7228300000000001</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.66557</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.8221499999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.68164</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.76151</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.68111</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.50356</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.67411</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.83745</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.018</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.51438</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.78934</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16128</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.15718</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>1.11311</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.12851</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.17921</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.76966</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45927</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40939</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.52567</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.05541</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.0215</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.18129</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.80765</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.12993</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.13881</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07164</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09275</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.07874</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.24603</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.10409</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.2707</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.07544</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.77774</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.7739299999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.55898</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.11674</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.70365</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.53259</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.60902</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.60684</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.5993200000000001</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33841</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.44032</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.63948</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.55798</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.68187</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.07064</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.98345</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.83021</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.1738</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.64628</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.9333400000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.1528</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.09257</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.1769</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.09402</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.6315499999999999</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.96827</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.00164</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.13123</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.02909</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.7767500000000001</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.7407100000000001</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.1596</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.7133700000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.11367</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.13525</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.72677</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.9939</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.9884700000000001</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.82601</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.08262</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.15338</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.13835</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.13503</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.16771</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18071</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.13172</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.13959</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.13844</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.10523</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.8687</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.70123</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.4903</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72811</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31194</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.57582</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49269</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.25166</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.18539</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.24554</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.50657</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.18959</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.18505</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.50657</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18539</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.27414</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25856</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24598</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.19547</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.1857</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.6156699999999999</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.49111</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48317</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48842</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.4895</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.60192</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.49209</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48685</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34631</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.18651</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.96605</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.9908899999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5902500000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.56431</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.4137</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27785</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04595</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.16858</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00504</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20329</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04529</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15402</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05681</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.02162</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>0.70156</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.16612</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>0.70156</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.5926399999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.16735</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.24677</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.63195</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.78085</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.70282</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.70614</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.7807999999999999</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.8062999999999999</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.8512999999999999</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.79027</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.9444199999999999</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.5325</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.8176599999999999</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.47859</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35562</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33734</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.39059</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.27798</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.8141799999999999</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1.17085</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>1.30253</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>1.1081</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>1.17789</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>1.38069</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.6975399999999999</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.49234</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.74085</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.7313999999999999</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.89528</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.20993</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.2445</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.67013</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72675</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.63326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.7281</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.8135</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7824099999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.74126</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.02245</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40524</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8424400000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.4378</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.58476</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.8101699999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.3943</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.03331</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.38843</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.77917</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.45327</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7885800000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8127799999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79492</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88532</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.51363</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42578</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47312</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23287</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54453</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50492</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45091</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42109</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40345</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37508</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5956900000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.54896</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.58349</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.11742</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43253</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.63385</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.81729</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.30901</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.28284</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.31021</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5606100000000001</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.82505</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48193</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.54979</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.98111</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.57001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.50336</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.9797</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.81053</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78549</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.70735</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.59684</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.58328</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.61983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.6908200000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.5843200000000001</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.6191599999999999</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.71473</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.58241</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.62371</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.61205</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.52525</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.6016699999999999</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.6357999999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7603300000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.6191599999999999</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.74185</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.63426</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.61971</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.62502</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.60687</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.59005</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.63901</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.58838</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.49102</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95108</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.49932</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.56023</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.70984</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.4086</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.61025</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.8469500000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.7261599999999999</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.94208</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.10092</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1.15978</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.50317</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.4092</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8095399999999999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.89813</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.83272</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.90365</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.80231</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.9463400000000001</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.55875</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.48604</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.8694500000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.48086</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.8593999999999999</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.78284</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.80462</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.60625</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.99142</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.47585</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.48261</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.51581</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.47073</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.08032</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.74848</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.37007</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70269</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79413</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6489299999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58282</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.68196</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.7430099999999999</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.15892</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.18979</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>1.33715</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.57348</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>1.39408</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.50026</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.60925</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.37992</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.62211</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.17035</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.6367</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.58609</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.4168</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.40039</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.3972</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.97577</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.95635</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.54485</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.8469</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>1.13229</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>1.01933</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.15025</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.73508</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1.58058</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.69927</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.64742</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.4494</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>1.27747</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.48098</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>1.36712</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.44008</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.46671</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>1.33204</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.35546</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.40281</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.46366</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>1.30115</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>1.28034</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.47001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>1.37547</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.41851</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>1.15292</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.5483300000000001</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.51349</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.42344</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3248</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.39489</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.27617</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24662</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.28329</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.55065</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.7837000000000001</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.20403</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.38679</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.7569</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.74638</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.74527</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.7451599999999999</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.75264</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.47808</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43805</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.59105</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.52611</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.64842</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.88859</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.22698</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45754</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.72446</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9930800000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.56355</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49996</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.59196</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.74595</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.74521</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.7336</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.73451</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.64679</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.41514</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.9903999999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.3967</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.60246</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.07098</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.79604</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.78604</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>1.21024</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.7085</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.63978</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.15075</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.77534</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.8943300000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.06993</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.44462</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.42962</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.46249</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.47486</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.46992</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.44659</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.46962</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.1945</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.50473</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.73737</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.58538</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.61834</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.50124</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.5096499999999999</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.51706</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.45218</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.55134</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.07016</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.4668</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.50364</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.25003</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.82689</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.58227</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.52718</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.67546</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.63803</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5400199999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.41558</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.69281</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.96316</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.02742</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32609</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.59051</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.48447</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.44505</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.7457</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.27271</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.94796</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.94133</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.79862</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45763</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.42055</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50331</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.44678</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34923</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.49246</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.42677</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.7026399999999999</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.67935</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>1.02773</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.7232000000000001</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.59077</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.18873</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.43603</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5681900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.6232300000000001</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.48469</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.41867</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>1.40999</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.63867</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.82196</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6411100000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.81751</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46799</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.52911</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.43063</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5793200000000001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7915</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.8011200000000001</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.24155</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.1885</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.58897</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5140399999999999</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.79323</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.79871</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.57635</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51606</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.06559</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.59033</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.53052</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.1869</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.19336</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.08693</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.85161</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.89627</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.38453</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.9693099999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.56585</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.8040499999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.0088</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.70939</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.94304</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.17882</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.8979400000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.65827</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.37361</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.4729100000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.713</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.8077799999999999</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.97473</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.8862000000000001</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.63348</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.17524</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.04171</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.0271</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.47233</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-0.02524</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.2038</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.89344</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.65219</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.0391</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.22607</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.53308</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.7462000000000001</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.11939</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.5655399999999999</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.53765</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.65872</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.67631</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.9341499999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.1869</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.83466</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>1.19888</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.8492999999999999</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>1.21736</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>1.19364</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.27748</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.237</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.92638</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.92988</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.30717</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.48795</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.70939</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.62482</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.02077</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.74982</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.56646</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.69666</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.83261</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47597</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.34174</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.71275</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45618</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43091</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.52763</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.60648</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.46092</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.82943</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.59285</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.56356</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69683</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.58915</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.48087</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.02288</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5239</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.99866</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.53546</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.58166</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42704</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.22231</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.60162</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.56625</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.68183</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.70051</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.91298</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6398400000000001</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.8418600000000001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.50302</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.19745</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25729</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.26439</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.25448</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.29919</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.68408</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.5560499999999999</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.63598</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.39716</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43297</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.5922500000000001</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.20243</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25976</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20053</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.24702</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.18261</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.21144</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.17766</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.1966</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.17646</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.17154</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.19277</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.17892</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.17154</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.17892</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.43865</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.18015</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.22198</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.25997</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27944</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.64016</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.3274</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.8434299999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.8766900000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.42902</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.49402</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.55829</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.53006</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.6246699999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.5668500000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.92214</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.92669</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.46162</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.30523</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.1925</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.38489</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.48285</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27991</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.47116</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.42115</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.68532</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.46085</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>1.43189</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.48321</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.20521</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.03581</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.59234</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.48333</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.46254</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.02931</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.7936</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.3624</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>1.21221</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.19845</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.74136</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>1.24961</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.74852</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.02482</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.79187</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.11954</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.33533</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.25312</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.57373</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.221</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.78023</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.59622</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33768</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6411699999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.59862</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.60003</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.47369</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23016</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.50829</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5295700000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.45143</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.46073</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48366</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.83036</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.66371</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.57478</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.67614</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.58308</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.60729</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>1.18394</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.57126</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5784400000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.9198099999999999</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.87825</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.56589</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.53138</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.81041</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.42788</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.42022</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.43191</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.42313</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.43759</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.48162</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.47768</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.47791</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.44829</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.54142</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.48033</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.8633999999999999</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.67684</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.5135700000000001</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.45201</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.44237</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46569</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33951</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43471</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.52337</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.47345</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.7743099999999999</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.25689</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.64746</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.9065700000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.67959</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>1.1788</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>1.19991</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.53565</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>1.21393</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.59834</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.17232</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.69659</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.7649600000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.7464400000000001</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.99403</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.0181</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.04157</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.10204</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.09319</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.14936</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7463099999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.89386</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.6267200000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70236</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.58243</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.93159</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.86909</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.4592</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.9183300000000001</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.77544</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.81216</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.47121</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39296</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.62909</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.2847</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.40806</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.27117</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.25017</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.24817</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.86352</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.07154</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.9893200000000001</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.9925700000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.10419</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.01808</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.10204</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.08465</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.1149</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.11135</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.6695099999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.65206</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.22049</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.27402</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.18932</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70369</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.80055</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.17751</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.26325</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.25736</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.50836</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.34138</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.77456</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.53967</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.5403</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.67369</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.64378</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26742</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.60181</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.38084</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.05041</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9754400000000001</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.00241</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.02952</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.9953</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.9209299999999999</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.72139</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.07952</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.92999</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.7498400000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.38681</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5444199999999999</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.09685</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.09231</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.11539</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.09565</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.10758</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.1665</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.14808</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.99371</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.8715499999999999</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.79771</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.07562</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.22135</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.57293</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.11405</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.53087</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.90099</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.21904</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.23897</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.46937</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.27046</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.48246</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.7264</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.33121</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.50032</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.77302</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.73173</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.9773999999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.25333</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.18256</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.16988</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.24249</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.56044</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.7148300000000001</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>1.66095</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.9834400000000001</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.18694</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.19541</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.79728</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.93376</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.87476</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.6428200000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.57844</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.19069</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.15906</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.58397</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.39574</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.53757</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.95468</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.56091</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.42584</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.49146</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.49357</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.21379</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.63799</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>1.68888</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>1.78751</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1.74578</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.72343</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.42358</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.67035</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.34053</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.67551</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.86187</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.84394</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.8856799999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.8856799999999999</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8362999999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.8201799999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.8201799999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.8201799999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60899</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.8201799999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.8856799999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.8856799999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8856799999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.46346</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.46132</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.40704</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37241</v>
       </c>
     </row>
   </sheetData>
